--- a/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
+++ b/_downloads/6389148f3813c4a2cb904a2a4100c2de/data_query_matrix.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ6"/>
+  <dimension ref="A1:BK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -488,6 +488,7 @@
     <col width="50" customWidth="1" min="60" max="60"/>
     <col width="38" customWidth="1" min="61" max="61"/>
     <col width="50" customWidth="1" min="62" max="62"/>
+    <col width="50" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,6 +802,11 @@
           <t>SetJoin</t>
         </is>
       </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>InClause</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5318,6 +5324,168 @@
           </r>
         </is>
       </c>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>SELECT</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>FROM</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>table</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>WHERE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>column</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>IN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>val1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>val2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>val3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -10025,6 +10193,148 @@
           </r>
         </is>
       </c>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>let</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>found</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>:=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>$</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>val</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>val1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>val2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>val3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -11484,6 +11794,229 @@
           </r>
         </is>
       </c>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>query</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>users</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>filter</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>id_in</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>name</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -13359,6 +13892,179 @@
           </r>
         </is>
       </c>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>FILTER</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>?val</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>IN</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>v</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>l</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>v</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>l</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>v</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>l</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -13757,6 +14463,17 @@
               <rFont val="Consolas"/>
             </rPr>
             <t xml:space="preserve">(node(area); way(area););
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">node["amenity"~"^(restaurant|pub|cafe)$"];
 </t>
           </r>
         </is>
